--- a/Результаты замеров.xlsx
+++ b/Результаты замеров.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\Documents\Оля\Бауманка\Практика\3 курс\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\projects\bmstu\practic-2026-git\bmstu-practice-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="142">
   <si>
     <t>Minimum : 0s</t>
   </si>
@@ -120,9 +120,6 @@
   </si>
   <si>
     <t>826MB / 25.8MB</t>
-  </si>
-  <si>
-    <t>Minimum : 0</t>
   </si>
   <si>
     <t>46.8MiB</t>
@@ -802,12 +799,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="5" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="5" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
@@ -818,9 +809,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -835,7 +823,19 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="1" fillId="6" borderId="1" xfId="6" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="6" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="6" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="6" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="4" applyBorder="1" applyAlignment="1">
@@ -844,9 +844,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="6" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="6" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="40% — акцент1" xfId="4" builtinId="31"/>
@@ -1159,132 +1156,132 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="8"/>
-      <c r="N1" s="10" t="s">
+      <c r="L1" s="29"/>
+      <c r="N1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="O1" s="17" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="11" t="s">
         <v>17</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="L2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="O2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="12" t="s">
+      <c r="P2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="S2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="T2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="U2" s="13" t="s">
+      <c r="U2" s="11" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="15" t="s">
+      <c r="A3" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="B3" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="15" t="s">
+      <c r="E3" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="H3" s="16">
+      <c r="H3" s="14">
         <v>761</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="14" t="s">
+      <c r="N3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="O3" s="15" t="s">
+      <c r="O3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="P3" s="15" t="s">
+      <c r="P3" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="Q3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="R3" s="18" t="s">
+      <c r="R3" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="S3" s="15" t="s">
+      <c r="S3" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="T3" s="15" t="s">
+      <c r="T3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="U3" s="16">
+      <c r="U3" s="14">
         <v>742</v>
       </c>
     </row>
@@ -1293,223 +1290,223 @@
         <v>0</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="17" t="s">
         <v>26</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="N5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="O5" s="20" t="s">
+      <c r="O5" s="17" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="11" t="s">
         <v>17</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="N6" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="N6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="O6" s="12" t="s">
+      <c r="O6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="P6" s="12" t="s">
+      <c r="P6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="Q6" s="12" t="s">
+      <c r="Q6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="R6" s="12" t="s">
+      <c r="R6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="S6" s="12" t="s">
+      <c r="S6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="T6" s="12" t="s">
+      <c r="T6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="U6" s="13" t="s">
+      <c r="U6" s="11" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="18" t="s">
+      <c r="D7" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" s="16">
+      <c r="G7" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="14">
         <v>761</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="N7" s="14" t="s">
+      <c r="N7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="O7" s="15" t="s">
+      <c r="O7" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="P7" s="15" t="s">
+      <c r="P7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="Q7" s="15" t="s">
+      <c r="Q7" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="R7" s="18" t="s">
+      <c r="R7" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="S7" s="15" t="s">
+      <c r="S7" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="T7" s="15" t="s">
+      <c r="T7" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="U7" s="16">
+      <c r="U7" s="14">
         <v>742</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="C9" s="32" t="s">
+      <c r="B9" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="E9" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="F9" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="G9" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="O9" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="P9" s="21" t="s">
+      <c r="O9" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="P9" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q9" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="R9" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="S9" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="Q9" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="R9" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="S9" s="21" t="s">
+      <c r="T9" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="T9" s="21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" s="31" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    </row>
+    <row r="10" spans="1:21" s="25" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="K12" s="28" t="s">
+      <c r="K12" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="L12" s="19"/>
-      <c r="N12" s="10" t="s">
+      <c r="L12" s="31"/>
+      <c r="N12" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="O12" s="20" t="s">
+      <c r="O12" s="17" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="H13" s="11" t="s">
         <v>17</v>
       </c>
       <c r="K13" s="3" t="s">
@@ -1518,309 +1515,309 @@
       <c r="L13" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N13" s="11" t="s">
+      <c r="N13" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="O13" s="12" t="s">
+      <c r="O13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="P13" s="12" t="s">
+      <c r="P13" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="Q13" s="12" t="s">
+      <c r="Q13" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="R13" s="12" t="s">
+      <c r="R13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="S13" s="12" t="s">
+      <c r="S13" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="T13" s="12" t="s">
+      <c r="T13" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="U13" s="13" t="s">
+      <c r="U13" s="11" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="G14" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="H14" s="16">
+      <c r="H14" s="14">
         <v>6</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="N14" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="O14" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="O14" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="P14" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q14" s="15" t="s">
+      <c r="P14" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="R14" s="18" t="s">
+      <c r="Q14" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="S14" s="15" t="s">
+      <c r="R14" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="T14" s="15" t="s">
+      <c r="S14" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="U14" s="16">
+      <c r="T14" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="U14" s="14">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K15" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L15" s="5" t="s">
+      <c r="L16" s="5" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
+      <c r="N16" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="O16" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="K16" s="1" t="s">
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="L16" s="5" t="s">
+      <c r="L17" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="N16" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="O16" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="N17" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="O17" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="P17" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="Q17" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="R17" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="S17" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="T17" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="13" t="s">
+      <c r="U17" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="K17" s="1" t="s">
+    </row>
+    <row r="18" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="H18" s="14">
+        <v>6</v>
+      </c>
+      <c r="K18" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="L17" s="25" t="s">
+      <c r="L18" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="N17" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="O17" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="P17" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q17" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="R17" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S17" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="T17" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="U17" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G18" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H18" s="16">
-        <v>6</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="N18" s="14" t="s">
+      <c r="N18" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="O18" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="O18" s="15" t="s">
+      <c r="P18" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="P18" s="15" t="s">
+      <c r="Q18" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="Q18" s="15" t="s">
+      <c r="R18" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="R18" s="18" t="s">
+      <c r="S18" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="S18" s="15" t="s">
+      <c r="T18" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="T18" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="U18" s="16">
+      <c r="U18" s="14">
         <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="C20" s="27">
+      <c r="B20" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="24">
         <v>-2.0000000000000001E-4</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="F20" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="F20" s="23" t="s">
+      <c r="G20" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="G20" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="O20" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="P20" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q20" s="23" t="s">
+      <c r="O20" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="P20" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q20" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="R20" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="S20" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="R20" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="S20" s="23" t="s">
+      <c r="T20" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="T20" s="23" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" s="31" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    </row>
+    <row r="22" spans="1:21" s="25" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="K24" s="29" t="s">
+      <c r="K24" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="L24" s="30"/>
-      <c r="N24" s="10" t="s">
+      <c r="L24" s="33"/>
+      <c r="N24" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="O24" s="20" t="s">
+      <c r="O24" s="17" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G25" s="12" t="s">
+      <c r="G25" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="H25" s="11" t="s">
         <v>17</v>
       </c>
       <c r="K25" s="3" t="s">
@@ -1829,275 +1826,277 @@
       <c r="L25" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N25" s="11" t="s">
+      <c r="N25" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="O25" s="12" t="s">
+      <c r="O25" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="P25" s="12" t="s">
+      <c r="P25" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="Q25" s="12" t="s">
+      <c r="Q25" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="R25" s="12" t="s">
+      <c r="R25" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="S25" s="12" t="s">
+      <c r="S25" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="T25" s="12" t="s">
+      <c r="T25" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="U25" s="13" t="s">
+      <c r="U25" s="11" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="C26" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26" s="18" t="s">
+      <c r="D26" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="15" t="s">
+      <c r="E26" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="G26" s="15" t="s">
+      <c r="F26" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="H26" s="16">
+      <c r="G26" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" s="14">
         <v>141</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N26" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="O26" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="O26" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="P26" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q26" s="15" t="s">
+      <c r="P26" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="R26" s="18" t="s">
+      <c r="Q26" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="S26" s="15" t="s">
+      <c r="R26" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="T26" s="15" t="s">
+      <c r="S26" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="U26" s="16">
+      <c r="T26" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="U26" s="14">
         <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K27" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="K28" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="L27" s="5" t="s">
+      <c r="L28" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="9" t="s">
+      <c r="N28" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="O28" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="K28" s="1" t="s">
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="L28" s="5" t="s">
+      <c r="L29" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="N28" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="O28" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+      <c r="N29" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="O29" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="P29" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="Q29" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="R29" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F29" s="12" t="s">
+      <c r="S29" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G29" s="12" t="s">
+      <c r="T29" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H29" s="13" t="s">
+      <c r="U29" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="K29" s="1" t="s">
+    </row>
+    <row r="30" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H30" s="14">
+        <v>143</v>
+      </c>
+      <c r="K30" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="L29" s="5" t="s">
+      <c r="L30" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="N29" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="O29" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="P29" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q29" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="R29" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="S29" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="T29" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="U29" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="G30" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="H30" s="16">
-        <v>143</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="L30" s="6" t="s">
+      <c r="N30" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="N30" s="14" t="s">
+      <c r="O30" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="O30" s="15" t="s">
+      <c r="P30" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="P30" s="15" t="s">
+      <c r="Q30" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="Q30" s="15" t="s">
+      <c r="R30" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="R30" s="18" t="s">
+      <c r="S30" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="S30" s="15" t="s">
+      <c r="T30" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="T30" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="U30" s="16">
+      <c r="U30" s="14">
         <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="C32" s="23" t="s">
+      <c r="B32" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="E32" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="F32" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="F32" s="23" t="s">
+      <c r="G32" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="G32" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="H32" s="23">
+      <c r="H32" s="20">
         <v>2</v>
       </c>
-      <c r="O32" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="P32" s="26">
+      <c r="O32" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="P32" s="23">
         <v>-2.8E-3</v>
       </c>
-      <c r="Q32" s="23" t="s">
+      <c r="Q32" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="R32" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="R32" s="24" t="s">
+      <c r="S32" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="S32" s="23" t="s">
+      <c r="T32" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="T32" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="U32" s="21">
+      <c r="U32" s="18">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="K1:L1"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="K24:L24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Результаты замеров.xlsx
+++ b/Результаты замеров.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="144">
   <si>
     <t>Minimum : 0s</t>
   </si>
@@ -44,15 +44,6 @@
     <t>Elasticsearch</t>
   </si>
   <si>
-    <t>Average : 805.188µs</t>
-  </si>
-  <si>
-    <t>Maximum : 2.6498ms</t>
-  </si>
-  <si>
-    <t>QPS : 1243.726433469413</t>
-  </si>
-  <si>
     <t>docker stats --no-stream</t>
   </si>
   <si>
@@ -188,33 +179,6 @@
     <t>0 / 1.35MB</t>
   </si>
   <si>
-    <t>Average : 3.789285ms</t>
-  </si>
-  <si>
-    <t>Minimum : 1.5113ms</t>
-  </si>
-  <si>
-    <t>Maximum : 148.9161ms</t>
-  </si>
-  <si>
-    <t>Total : 3.7854965s</t>
-  </si>
-  <si>
-    <t>QPS : 263.9019742852754</t>
-  </si>
-  <si>
-    <t>Total : 873.8382ms</t>
-  </si>
-  <si>
-    <t>Maximum : 6.1334ms</t>
-  </si>
-  <si>
-    <t>Average : 874.712µs</t>
-  </si>
-  <si>
-    <t>QPS : 1143.2322368145499</t>
-  </si>
-  <si>
     <t>dac4c3fb8fc5</t>
   </si>
   <si>
@@ -227,45 +191,9 @@
     <t>1.01%</t>
   </si>
   <si>
-    <t>1.683GiB / 15.54GiB</t>
-  </si>
-  <si>
-    <t>10.83%</t>
-  </si>
-  <si>
-    <t>629kB / 1.44MB</t>
-  </si>
-  <si>
-    <t>296MB / 610kB</t>
-  </si>
-  <si>
-    <t>295MB / 594kB</t>
-  </si>
-  <si>
-    <t>315kB / 720kB</t>
-  </si>
-  <si>
-    <t>10.67%</t>
-  </si>
-  <si>
-    <t>1.657GiB / 15.54GiB</t>
-  </si>
-  <si>
     <t>0.23%</t>
   </si>
   <si>
-    <t>26.6MiB</t>
-  </si>
-  <si>
-    <t>0.16%</t>
-  </si>
-  <si>
-    <t>314kB / 720kB</t>
-  </si>
-  <si>
-    <t>1MB / 16 kB</t>
-  </si>
-  <si>
     <t>Average : 6.656067ms</t>
   </si>
   <si>
@@ -290,63 +218,12 @@
     <t>0.58%</t>
   </si>
   <si>
-    <t>1.597GiB / 15.54GiB</t>
-  </si>
-  <si>
-    <t>10.28%</t>
-  </si>
-  <si>
-    <t>796kB / 1.65MB</t>
-  </si>
-  <si>
-    <t>12.3kB / 647kB</t>
-  </si>
-  <si>
-    <t>0B / 475kB</t>
-  </si>
-  <si>
-    <t>452kB / 938kB</t>
-  </si>
-  <si>
-    <t>10.23%</t>
-  </si>
-  <si>
-    <t>1.59GiB / 15.54GiB</t>
-  </si>
-  <si>
     <t>0.86%</t>
   </si>
   <si>
-    <t>Total : 816.1517ms</t>
-  </si>
-  <si>
-    <t>7MiB</t>
-  </si>
-  <si>
     <t>0.05%</t>
   </si>
   <si>
-    <t>344kB / 712kB</t>
-  </si>
-  <si>
-    <t>12.3kB / 172kB</t>
-  </si>
-  <si>
-    <t>Average : 1.759243ms</t>
-  </si>
-  <si>
-    <t>Minimum : 510.8µs</t>
-  </si>
-  <si>
-    <t>Maximum : 39.7514ms</t>
-  </si>
-  <si>
-    <t>Total : 1.7574842s</t>
-  </si>
-  <si>
-    <t>QPS : 568.4261628070398</t>
-  </si>
-  <si>
     <t>81.7MB / 61.4kB</t>
   </si>
   <si>
@@ -410,46 +287,175 @@
     <t>928kB / 1.05MB</t>
   </si>
   <si>
-    <t>0B / 590kB</t>
-  </si>
-  <si>
     <t>619kB / 700kB</t>
   </si>
   <si>
-    <t xml:space="preserve">0.92% </t>
-  </si>
-  <si>
-    <t>146.8MiB / 15.54GiB</t>
-  </si>
-  <si>
     <t>0.00%</t>
   </si>
   <si>
-    <t>Average : 202.603756ms</t>
-  </si>
-  <si>
-    <t>Minimum : 999.4µs</t>
-  </si>
-  <si>
-    <t>Maximum : 325.2709ms</t>
-  </si>
-  <si>
-    <t>Total : 3m22.4011523s</t>
-  </si>
-  <si>
-    <t>QPS : 4.935742650907823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9MiB </t>
-  </si>
-  <si>
     <t>291kB / 350kB</t>
   </si>
   <si>
-    <t>0 / 0</t>
-  </si>
-  <si>
     <t>delta</t>
+  </si>
+  <si>
+    <t>Average : 862.343µs</t>
+  </si>
+  <si>
+    <t>Maximum : 4.011ms</t>
+  </si>
+  <si>
+    <t>Total : 862.3438ms</t>
+  </si>
+  <si>
+    <t>QPS : 1159.6303005831317</t>
+  </si>
+  <si>
+    <t>Average : 885.472µs</t>
+  </si>
+  <si>
+    <t>Minimum : 0.00000</t>
+  </si>
+  <si>
+    <t>Maximum : 3.2142ms</t>
+  </si>
+  <si>
+    <t>Total : 885.4721ms</t>
+  </si>
+  <si>
+    <t>QPS : 1129.3410599837082</t>
+  </si>
+  <si>
+    <t>Average : 1.322829ms</t>
+  </si>
+  <si>
+    <t>Minimum : 511.9µs</t>
+  </si>
+  <si>
+    <t>Maximum : 3.2605ms</t>
+  </si>
+  <si>
+    <t>Total : 1.3228292s</t>
+  </si>
+  <si>
+    <t>QPS : 755.9554929691603</t>
+  </si>
+  <si>
+    <t>Average : 194.055427ms</t>
+  </si>
+  <si>
+    <t>Minimum : 709.6µs</t>
+  </si>
+  <si>
+    <t>Maximum : 310.5193ms</t>
+  </si>
+  <si>
+    <t>Total : 3m14.0554278s</t>
+  </si>
+  <si>
+    <t>QPS : 5.153166862359725</t>
+  </si>
+  <si>
+    <t>18.9MiB / 15.54GiB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.6MiB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12% </t>
+  </si>
+  <si>
+    <t>0.81%</t>
+  </si>
+  <si>
+    <t>0B / 28.7kB</t>
+  </si>
+  <si>
+    <t>0B / 586kB</t>
+  </si>
+  <si>
+    <t>0 / 557.3kB</t>
+  </si>
+  <si>
+    <t>Average : 1.626976ms</t>
+  </si>
+  <si>
+    <t>Minimum : 509.4µs</t>
+  </si>
+  <si>
+    <t>Maximum : 5.7766ms</t>
+  </si>
+  <si>
+    <t>Total : 1.6269762s</t>
+  </si>
+  <si>
+    <t>QPS : 614.6371409735434</t>
+  </si>
+  <si>
+    <t>9.67%</t>
+  </si>
+  <si>
+    <t>10.08%</t>
+  </si>
+  <si>
+    <t>0.41%</t>
+  </si>
+  <si>
+    <t>1.566GiB / 15.54GiB</t>
+  </si>
+  <si>
+    <t>1.502GiB / 15.54GiB</t>
+  </si>
+  <si>
+    <t>0.064GiB</t>
+  </si>
+  <si>
+    <t>324kB / 496kB</t>
+  </si>
+  <si>
+    <t>323kB / 496kB</t>
+  </si>
+  <si>
+    <t>0B / 479kB</t>
+  </si>
+  <si>
+    <t>0B / 618kB</t>
+  </si>
+  <si>
+    <t>0MB / 139kB</t>
+  </si>
+  <si>
+    <t>1.501GiB / 15.54GiB</t>
+  </si>
+  <si>
+    <t>1.561GiB / 15.54GiB</t>
+  </si>
+  <si>
+    <t>0.06GiB</t>
+  </si>
+  <si>
+    <t>9.66%</t>
+  </si>
+  <si>
+    <t>10.04%</t>
+  </si>
+  <si>
+    <t>0.38%</t>
+  </si>
+  <si>
+    <t>1.17kB / 126kB</t>
+  </si>
+  <si>
+    <t>354kB / 496kB</t>
+  </si>
+  <si>
+    <t>353kB / 370kB</t>
+  </si>
+  <si>
+    <t>0B / 455kB</t>
+  </si>
+  <si>
+    <t>0B / 24kB</t>
   </si>
 </sst>
 </file>
@@ -1157,46 +1163,46 @@
   <sheetData>
     <row r="1" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K1" s="28" t="s">
         <v>1</v>
       </c>
       <c r="L1" s="29"/>
       <c r="N1" s="8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O1" s="17" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="E2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="F2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="G2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="H2" s="11" t="s">
         <v>14</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>17</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>2</v>
@@ -1205,81 +1211,81 @@
         <v>3</v>
       </c>
       <c r="N2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="R2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="S2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="T2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="U2" s="11" t="s">
         <v>14</v>
-      </c>
-      <c r="S2" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="T2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="U2" s="11" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="E3" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="16" t="s">
+      <c r="F3" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>46</v>
-      </c>
       <c r="G3" s="13" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H3" s="14">
         <v>761</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="N3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="R3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="S3" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="Q3" s="13" t="s">
+      <c r="T3" s="13" t="s">
         <v>21</v>
-      </c>
-      <c r="R3" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="S3" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="T3" s="13" t="s">
-        <v>24</v>
       </c>
       <c r="U3" s="14">
         <v>742</v>
@@ -1290,136 +1296,136 @@
         <v>0</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O5" s="17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="E6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="F6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="G6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="H6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>17</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="P6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="R6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="P6" s="10" t="s">
+      <c r="S6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="Q6" s="10" t="s">
+      <c r="T6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="R6" s="10" t="s">
+      <c r="U6" s="11" t="s">
         <v>14</v>
-      </c>
-      <c r="S6" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="T6" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="U6" s="11" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C7" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="E7" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="13" t="s">
+      <c r="G7" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>48</v>
       </c>
       <c r="H7" s="14">
         <v>761</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="O7" s="13" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="P7" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q7" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="R7" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="S7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="Q7" s="13" t="s">
+      <c r="T7" s="13" t="s">
         <v>28</v>
-      </c>
-      <c r="R7" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="S7" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="T7" s="13" t="s">
-        <v>31</v>
       </c>
       <c r="U7" s="14">
         <v>742</v>
@@ -1428,86 +1434,86 @@
     <row r="8" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="27" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="C9" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="G9" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>53</v>
-      </c>
       <c r="O9" s="27" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="P9" s="18" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Q9" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="R9" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="S9" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="R9" s="19" t="s">
+      <c r="T9" s="18" t="s">
         <v>33</v>
-      </c>
-      <c r="S9" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="T9" s="18" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:21" s="25" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K12" s="30" t="s">
         <v>4</v>
       </c>
       <c r="L12" s="31"/>
       <c r="N12" s="8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="E13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="F13" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="G13" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="H13" s="11" t="s">
         <v>14</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>17</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>2</v>
@@ -1516,81 +1522,81 @@
         <v>3</v>
       </c>
       <c r="N13" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="O13" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="O13" s="10" t="s">
+      <c r="R13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="P13" s="10" t="s">
+      <c r="S13" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="Q13" s="10" t="s">
+      <c r="T13" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="R13" s="10" t="s">
+      <c r="U13" s="11" t="s">
         <v>14</v>
-      </c>
-      <c r="S13" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="T13" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="U13" s="11" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="H14" s="14">
         <v>6</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="Q14" s="13" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="R14" s="16" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="S14" s="13" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="T14" s="13" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="U14" s="14">
         <v>6</v>
@@ -1598,139 +1604,139 @@
     </row>
     <row r="15" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K15" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>134</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="E17" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="F17" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="G17" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="H17" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>17</v>
-      </c>
       <c r="K17" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="N17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="O17" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q17" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="O17" s="10" t="s">
+      <c r="R17" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="P17" s="10" t="s">
+      <c r="S17" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="Q17" s="10" t="s">
+      <c r="T17" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="R17" s="10" t="s">
+      <c r="U17" s="11" t="s">
         <v>14</v>
-      </c>
-      <c r="S17" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="T17" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="U17" s="11" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="H18" s="14">
         <v>6</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="P18" s="13" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="Q18" s="13" t="s">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="R18" s="16" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="S18" s="13" t="s">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="T18" s="13" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="U18" s="14">
         <v>6</v>
@@ -1739,86 +1745,86 @@
     <row r="19" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="27" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="C20" s="24">
         <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="O20" s="27" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="P20" s="20" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="Q20" s="20" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="R20" s="21" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="S20" s="20" t="s">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="T20" s="20" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:21" s="25" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:21" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K24" s="32" t="s">
         <v>5</v>
       </c>
       <c r="L24" s="33"/>
       <c r="N24" s="8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O24" s="17" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="E25" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="F25" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="G25" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="H25" s="11" t="s">
         <v>14</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>17</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>2</v>
@@ -1827,269 +1833,263 @@
         <v>3</v>
       </c>
       <c r="N25" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="O25" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="P25" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q25" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="O25" s="10" t="s">
+      <c r="R25" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="P25" s="10" t="s">
+      <c r="S25" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="Q25" s="10" t="s">
+      <c r="T25" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="R25" s="10" t="s">
+      <c r="U25" s="11" t="s">
         <v>14</v>
-      </c>
-      <c r="S25" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="T25" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="U25" s="11" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D26" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F26" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="E26" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>72</v>
-      </c>
       <c r="G26" s="13" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="H26" s="14">
         <v>141</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="N26" s="12" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="O26" s="13" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="P26" s="13" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="Q26" s="13" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="R26" s="16" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="S26" s="13" t="s">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="T26" s="13" t="s">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="U26" s="14">
-        <v>142</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K27" s="1" t="s">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>56</v>
+        <v>119</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="N28" s="7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O28" s="17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="E29" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="F29" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="G29" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="H29" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H29" s="11" t="s">
-        <v>17</v>
-      </c>
       <c r="K29" s="1" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="N29" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="O29" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q29" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="O29" s="10" t="s">
+      <c r="R29" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="P29" s="10" t="s">
+      <c r="S29" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="Q29" s="10" t="s">
+      <c r="T29" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="R29" s="10" t="s">
+      <c r="U29" s="11" t="s">
         <v>14</v>
-      </c>
-      <c r="S29" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="T29" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="U29" s="11" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>70</v>
+        <v>131</v>
       </c>
       <c r="H30" s="14">
         <v>143</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>58</v>
+        <v>121</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="O30" s="13" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="P30" s="13" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="Q30" s="13" t="s">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="R30" s="16" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="S30" s="13" t="s">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="T30" s="13" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="U30" s="14">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="27" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="H32" s="20">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="O32" s="27" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="P32" s="23">
         <v>-2.8E-3</v>
       </c>
       <c r="Q32" s="20" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="R32" s="21" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="S32" s="20" t="s">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="T32" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="U32" s="18">
-        <v>2</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
